--- a/data/trans_bre/P19C04-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P19C04-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,44; 2,21</t>
+          <t>-13,53; 3,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-18,1; -2,06</t>
+          <t>-18,84; -2,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,85; 1,22</t>
+          <t>-13,62; 0,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,03; 1,57</t>
+          <t>-7,73; 1,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-55,17; 13,97</t>
+          <t>-53,14; 21,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-52,77; -6,94</t>
+          <t>-54,99; -9,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-57,15; 6,88</t>
+          <t>-55,86; 3,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-46,84; 16,99</t>
+          <t>-46,58; 19,54</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,89; 1,6</t>
+          <t>-10,11; 1,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-16,76; -4,34</t>
+          <t>-15,93; -4,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-11,08; -0,18</t>
+          <t>-10,7; -0,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 3,89</t>
+          <t>-3,33; 3,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-37,04; 8,02</t>
+          <t>-37,27; 9,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-53,07; -17,85</t>
+          <t>-50,32; -15,92</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-52,35; -0,92</t>
+          <t>-49,56; -2,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-33,49; 69,8</t>
+          <t>-32,81; 69,34</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-15,47; -2,25</t>
+          <t>-15,72; -1,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-14,87; -1,1</t>
+          <t>-14,39; -0,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,88; 2,55</t>
+          <t>-7,29; 1,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,8; 2,45</t>
+          <t>-8,06; 2,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-60,38; -11,23</t>
+          <t>-60,88; -9,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-48,05; -4,03</t>
+          <t>-45,27; -2,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-51,3; 31,12</t>
+          <t>-53,0; 22,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-36,74; 16,49</t>
+          <t>-36,76; 19,5</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,87; 1,09</t>
+          <t>-10,55; 1,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-16,99; -3,51</t>
+          <t>-16,91; -3,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-16,07; -3,85</t>
+          <t>-16,27; -4,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-15,36; -2,56</t>
+          <t>-15,13; -3,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-52,09; 11,6</t>
+          <t>-54,93; 8,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-52,27; -14,66</t>
+          <t>-51,44; -15,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-59,88; -19,0</t>
+          <t>-60,39; -20,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-72,77; -22,23</t>
+          <t>-71,84; -24,33</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-14,2; 3,13</t>
+          <t>-15,11; 2,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15,36; 2,05</t>
+          <t>-15,72; 2,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,59; 7,83</t>
+          <t>-11,16; 7,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,67; -2,44</t>
+          <t>-13,48; -2,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-55,5; 20,04</t>
+          <t>-58,55; 12,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-46,85; 8,41</t>
+          <t>-46,24; 8,44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-45,45; 66,87</t>
+          <t>-52,05; 65,3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-54,79; -13,68</t>
+          <t>-55,47; -14,2</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-12,67; 1,18</t>
+          <t>-12,15; 1,34</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-18,08; -0,79</t>
+          <t>-17,18; -1,95</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-15,21; -0,58</t>
+          <t>-15,86; -0,47</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 5,94</t>
+          <t>-5,4; 5,8</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-61,67; 10,57</t>
+          <t>-61,55; 12,12</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-48,16; -2,13</t>
+          <t>-46,99; -6,41</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-48,01; -2,59</t>
+          <t>-48,98; -1,27</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-22,94; 35,19</t>
+          <t>-23,28; 34,35</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,96; 1,31</t>
+          <t>-8,93; 0,3</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,63; -2,53</t>
+          <t>-11,6; -2,5</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 1,26</t>
+          <t>-7,84; 1,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-11,76; -1,29</t>
+          <t>-10,78; -1,17</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-40,67; 7,5</t>
+          <t>-40,33; 2,44</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-50,83; -14,47</t>
+          <t>-51,16; -13,68</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-47,28; 11,76</t>
+          <t>-47,99; 14,53</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-74,86; -11,36</t>
+          <t>-76,34; -13,45</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-9,5; -0,77</t>
+          <t>-9,93; -1,03</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 2,7</t>
+          <t>-5,63; 2,5</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 0,94</t>
+          <t>-6,9; 1,07</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-10,86; 5,31</t>
+          <t>-10,65; 5,15</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-43,68; -4,47</t>
+          <t>-44,83; -5,53</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-28,99; 18,48</t>
+          <t>-30,54; 17,44</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-37,16; 6,37</t>
+          <t>-37,46; 7,85</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-50,09; 82,83</t>
+          <t>-49,45; 62,73</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-7,1; -3,19</t>
+          <t>-7,22; -3,2</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-9,28; -4,76</t>
+          <t>-9,4; -4,93</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,18; -3,01</t>
+          <t>-6,92; -3,01</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,13; -0,7</t>
+          <t>-6,44; -1,1</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-34,32; -17,24</t>
+          <t>-34,5; -17,02</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-35,81; -20,37</t>
+          <t>-35,84; -21,28</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-37,62; -17,67</t>
+          <t>-36,4; -17,75</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-39,83; -8,22</t>
+          <t>-40,93; -10,96</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P19C04-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P19C04-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-2,88</t>
+          <t>-4,92</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-21,58%</t>
+          <t>-32,02%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,53; 3,25</t>
+          <t>-12,12; 2,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-18,84; -2,89</t>
+          <t>-17,97; -1,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,62; 0,53</t>
+          <t>-13,55; 0,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 1,85</t>
+          <t>-9,7; -0,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-53,14; 21,47</t>
+          <t>-49,26; 18,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-54,99; -9,73</t>
+          <t>-53,5; -6,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-55,86; 3,96</t>
+          <t>-55,48; 4,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-46,58; 19,54</t>
+          <t>-53,08; -2,99</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,5</t>
+          <t>0,31</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-10,11; 1,74</t>
+          <t>-9,36; 0,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-15,93; -4,52</t>
+          <t>-16,48; -4,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-10,7; -0,64</t>
+          <t>-10,92; -0,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 3,82</t>
+          <t>-3,37; 3,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-37,27; 9,32</t>
+          <t>-35,94; 4,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-50,32; -15,92</t>
+          <t>-51,43; -17,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-49,56; -2,33</t>
+          <t>-51,42; 0,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-32,81; 69,34</t>
+          <t>-32,96; 60,56</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-2,44</t>
+          <t>-3,42</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-13,38%</t>
+          <t>-17,55%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-15,72; -1,93</t>
+          <t>-16,19; -2,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-14,39; -0,78</t>
+          <t>-14,62; -0,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 1,92</t>
+          <t>-7,54; 1,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,06; 2,8</t>
+          <t>-8,84; 2,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-60,88; -9,79</t>
+          <t>-63,24; -15,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-45,27; -2,83</t>
+          <t>-46,47; -2,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-53,0; 22,86</t>
+          <t>-55,9; 19,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-36,76; 19,5</t>
+          <t>-38,51; 12,34</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-8,1</t>
+          <t>-6,78</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-50,41%</t>
+          <t>-39,6%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,55; 1,01</t>
+          <t>-10,62; 0,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-16,91; -3,63</t>
+          <t>-17,15; -2,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-16,27; -4,29</t>
+          <t>-15,57; -3,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-15,13; -3,03</t>
+          <t>-13,17; -1,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-54,93; 8,46</t>
+          <t>-53,82; 8,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-51,44; -15,2</t>
+          <t>-52,69; -12,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-60,39; -20,48</t>
+          <t>-59,48; -17,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-71,84; -24,33</t>
+          <t>-60,26; -13,42</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-7,98</t>
+          <t>-8,81</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-37,92%</t>
+          <t>-39,26%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-15,11; 2,02</t>
+          <t>-14,31; 1,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15,72; 2,09</t>
+          <t>-15,91; 2,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,16; 7,45</t>
+          <t>-9,21; 8,16</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,48; -2,65</t>
+          <t>-14,07; -2,62</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-58,55; 12,4</t>
+          <t>-56,09; 10,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-46,24; 8,44</t>
+          <t>-46,83; 10,04</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-52,05; 65,3</t>
+          <t>-43,69; 74,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-55,47; -14,2</t>
+          <t>-55,02; -13,33</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,03</t>
+          <t>-0,0</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>-0,02%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-12,15; 1,34</t>
+          <t>-12,79; 1,05</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-17,18; -1,95</t>
+          <t>-16,68; -1,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-15,86; -0,47</t>
+          <t>-16,07; -0,75</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 5,8</t>
+          <t>-5,15; 5,84</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-61,55; 12,12</t>
+          <t>-60,98; 9,9</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-46,99; -6,41</t>
+          <t>-46,1; -5,03</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-48,98; -1,27</t>
+          <t>-49,88; -3,06</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-23,28; 34,35</t>
+          <t>-22,0; 35,62</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-5,14</t>
+          <t>-3,21</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-41,95%</t>
+          <t>-25,85%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,93; 0,3</t>
+          <t>-9,14; 0,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,6; -2,5</t>
+          <t>-11,78; -2,79</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 1,45</t>
+          <t>-7,51; 1,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,78; -1,17</t>
+          <t>-6,82; -0,02</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-40,33; 2,44</t>
+          <t>-40,46; 2,83</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-51,16; -13,68</t>
+          <t>-52,2; -15,3</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-47,99; 14,53</t>
+          <t>-48,15; 9,98</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-76,34; -13,45</t>
+          <t>-45,6; 0,05</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-4,16</t>
+          <t>-10,15</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-26,67%</t>
+          <t>-46,28%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-9,93; -1,03</t>
+          <t>-9,59; -0,83</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 2,5</t>
+          <t>-5,36; 2,86</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-6,9; 1,07</t>
+          <t>-7,38; 0,76</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-10,65; 5,15</t>
+          <t>-13,81; -6,72</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-44,83; -5,53</t>
+          <t>-44,76; -5,13</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-30,54; 17,44</t>
+          <t>-27,88; 20,42</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-37,46; 7,85</t>
+          <t>-38,76; 5,41</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-49,45; 62,73</t>
+          <t>-57,26; -33,6</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-3,95</t>
+          <t>-4,86</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-27,28%</t>
+          <t>-29,71%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-7,22; -3,2</t>
+          <t>-7,41; -3,12</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-9,4; -4,93</t>
+          <t>-9,42; -5,04</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,92; -3,01</t>
+          <t>-6,86; -2,82</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,44; -1,1</t>
+          <t>-6,35; -3,26</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-34,5; -17,02</t>
+          <t>-34,97; -16,54</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-35,84; -21,28</t>
+          <t>-36,04; -21,28</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-36,4; -17,75</t>
+          <t>-36,39; -17,49</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-40,93; -10,96</t>
+          <t>-36,63; -21,18</t>
         </is>
       </c>
     </row>
